--- a/output/P8.xlsx
+++ b/output/P8.xlsx
@@ -2452,15 +2452,16 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Base directory for this skill: /tmp/claude-1000/bundled-skills/2.1.246/5a1af67a935231f57f6359383ff53892/dataviz
 # Data Visualization
@@ -2560,7 +2561,6 @@
 | `scripts/validate_palette.js` | Runnable six-checks validator (run it; don't eyeball) |</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
